--- a/입출력 결선도.xlsx
+++ b/입출력 결선도.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sozx2\OneDrive\바탕 화면\plc_test\0708\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D163C51E-23D9-4B1A-AEF5-A97A98D494A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="312">
   <si>
     <t>센서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -947,12 +946,183 @@
   <si>
     <t>테스_종료</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공급후</t>
+  </si>
+  <si>
+    <t>Bit</t>
+  </si>
+  <si>
+    <t>X0</t>
+  </si>
+  <si>
+    <t>공급전</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>드릴상</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>드릴하</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>송출후</t>
+  </si>
+  <si>
+    <t>X4</t>
+  </si>
+  <si>
+    <t>송출전</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>배출후</t>
+  </si>
+  <si>
+    <t>X6</t>
+  </si>
+  <si>
+    <t>배출전</t>
+  </si>
+  <si>
+    <t>X7</t>
+  </si>
+  <si>
+    <t>매거진</t>
+  </si>
+  <si>
+    <t>X8</t>
+  </si>
+  <si>
+    <t>비금속</t>
+  </si>
+  <si>
+    <t>X9</t>
+  </si>
+  <si>
+    <t>금속</t>
+  </si>
+  <si>
+    <t>X0A</t>
+  </si>
+  <si>
+    <t>공급전솔</t>
+  </si>
+  <si>
+    <t>Y20</t>
+  </si>
+  <si>
+    <t>공급후솔</t>
+  </si>
+  <si>
+    <t>Y21</t>
+  </si>
+  <si>
+    <t>드릴온</t>
+  </si>
+  <si>
+    <t>Y22</t>
+  </si>
+  <si>
+    <t>송출전솔</t>
+  </si>
+  <si>
+    <t>Y23</t>
+  </si>
+  <si>
+    <t>송출후솔</t>
+  </si>
+  <si>
+    <t>Y24</t>
+  </si>
+  <si>
+    <t>배출전솔</t>
+  </si>
+  <si>
+    <t>Y25</t>
+  </si>
+  <si>
+    <t>배출후솔</t>
+  </si>
+  <si>
+    <t>Y26</t>
+  </si>
+  <si>
+    <t>컨베이어</t>
+  </si>
+  <si>
+    <t>Y27</t>
+  </si>
+  <si>
+    <t>가공드릴</t>
+  </si>
+  <si>
+    <t>Y28</t>
+  </si>
+  <si>
+    <t>적색</t>
+  </si>
+  <si>
+    <t>Y29</t>
+  </si>
+  <si>
+    <t>황색</t>
+  </si>
+  <si>
+    <t>Y2A</t>
+  </si>
+  <si>
+    <t>녹색</t>
+  </si>
+  <si>
+    <t>Y2B</t>
+  </si>
+  <si>
+    <t>pb1</t>
+  </si>
+  <si>
+    <t>X10</t>
+  </si>
+  <si>
+    <t>pb2</t>
+  </si>
+  <si>
+    <t>X11</t>
+  </si>
+  <si>
+    <t>pb3</t>
+  </si>
+  <si>
+    <t>X12</t>
+  </si>
+  <si>
+    <t>비상정지</t>
+  </si>
+  <si>
+    <t>X13</t>
+  </si>
+  <si>
+    <t>초기화</t>
+  </si>
+  <si>
+    <t>X14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -970,7 +1140,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1013,8 +1183,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1268,13 +1444,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1368,6 +1559,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1395,14 +1595,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1683,15 +1904,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:V45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:V76"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.875" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.125" customWidth="1"/>
-    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="6" max="6" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.875" customWidth="1"/>
     <col min="10" max="10" width="7.875" bestFit="1" customWidth="1"/>
@@ -1708,32 +1929,32 @@
   <sheetData>
     <row r="3" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35" t="s">
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="35"/>
+      <c r="H4" s="38"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="39"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="42"/>
     </row>
     <row r="5" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
@@ -2676,14 +2897,14 @@
       <c r="L31" s="20"/>
     </row>
     <row r="32" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H32" s="40"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="37" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="13">
@@ -2698,16 +2919,16 @@
       <c r="G33" s="13">
         <v>1</v>
       </c>
-      <c r="H33" s="42">
+      <c r="H33" s="33">
         <v>8</v>
       </c>
-      <c r="I33" s="42">
+      <c r="I33" s="33">
         <v>4</v>
       </c>
-      <c r="J33" s="42">
+      <c r="J33" s="33">
         <v>2</v>
       </c>
-      <c r="K33" s="42">
+      <c r="K33" s="33">
         <v>1</v>
       </c>
       <c r="L33" s="13">
@@ -2722,12 +2943,12 @@
       <c r="O33" s="13">
         <v>1</v>
       </c>
-      <c r="P33" s="31" t="s">
+      <c r="P33" s="34" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C34" s="36"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="11" t="s">
         <v>89</v>
       </c>
@@ -2764,10 +2985,10 @@
       <c r="O34" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="P34" s="32"/>
+      <c r="P34" s="35"/>
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C35" s="36"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="11" t="s">
         <v>87</v>
       </c>
@@ -2804,7 +3025,7 @@
       <c r="O35" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="P35" s="33"/>
+      <c r="P35" s="36"/>
     </row>
     <row r="36" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C36" s="14">
@@ -3040,6 +3261,343 @@
       <c r="O45" s="17"/>
       <c r="P45" s="19"/>
     </row>
+    <row r="48" spans="3:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D49" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="F49" s="43"/>
+      <c r="G49" s="50" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D50" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="E50" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" s="10"/>
+      <c r="G50" s="51" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="51" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D51" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F51" s="10"/>
+      <c r="G51" s="51" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="52" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D52" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="E52" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F52" s="10"/>
+      <c r="G52" s="51" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="53" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D53" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="E53" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="51" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D54" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="51" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="55" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D55" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="E55" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F55" s="10"/>
+      <c r="G55" s="51" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D56" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="E56" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F56" s="10"/>
+      <c r="G56" s="51" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="57" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D57" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E57" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F57" s="10"/>
+      <c r="G57" s="51" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="58" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D58" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="E58" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F58" s="10"/>
+      <c r="G58" s="51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D59" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E59" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F59" s="10"/>
+      <c r="G59" s="51" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="60" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D60" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="E60" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F60" s="10"/>
+      <c r="G60" s="51" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="61" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D61" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="E61" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F61" s="10"/>
+      <c r="G61" s="51" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="62" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D62" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="E62" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F62" s="10"/>
+      <c r="G62" s="51" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="63" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D63" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="E63" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F63" s="10"/>
+      <c r="G63" s="51" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="64" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D64" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F64" s="10"/>
+      <c r="G64" s="51" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="65" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D65" s="45" t="s">
+        <v>288</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F65" s="10"/>
+      <c r="G65" s="51" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="66" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D66" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="E66" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F66" s="10"/>
+      <c r="G66" s="51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D67" s="45" t="s">
+        <v>292</v>
+      </c>
+      <c r="E67" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F67" s="10"/>
+      <c r="G67" s="51" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D68" s="45" t="s">
+        <v>294</v>
+      </c>
+      <c r="E68" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F68" s="10"/>
+      <c r="G68" s="51" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="69" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D69" s="45" t="s">
+        <v>296</v>
+      </c>
+      <c r="E69" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F69" s="10"/>
+      <c r="G69" s="51" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="70" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D70" s="45" t="s">
+        <v>298</v>
+      </c>
+      <c r="E70" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F70" s="10"/>
+      <c r="G70" s="51" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="71" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D71" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="E71" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F71" s="10"/>
+      <c r="G71" s="51" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="72" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D72" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="E72" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F72" s="10"/>
+      <c r="G72" s="51" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="73" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D73" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="E73" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F73" s="10"/>
+      <c r="G73" s="51" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="74" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D74" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="E74" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F74" s="10"/>
+      <c r="G74" s="51" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="75" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D75" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="E75" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="F75" s="10"/>
+      <c r="G75" s="51" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="76" spans="4:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D76" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="E76" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="52" t="s">
+        <v>311</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="P33:P35"/>

--- a/입출력 결선도.xlsx
+++ b/입출력 결선도.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="7380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="364">
   <si>
     <t>센서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1117,6 +1117,214 @@
   </si>
   <si>
     <t>X14</t>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공_후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공_전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드_상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴하강</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드_하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송_전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송_후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배_전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배_후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스_하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스_상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흡_전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흡_후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y2A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창_후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y2B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창_전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sol13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>용량형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y2D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유도형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y2F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1465,7 +1673,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1568,6 +1776,36 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1595,35 +1833,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1905,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:V76"/>
+  <dimension ref="C3:W76"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
@@ -1929,32 +2140,32 @@
   <sheetData>
     <row r="3" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38" t="s">
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="38"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="21"/>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="42"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="52"/>
     </row>
     <row r="5" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
@@ -2903,8 +3114,8 @@
       <c r="K32" s="32"/>
       <c r="L32" s="32"/>
     </row>
-    <row r="33" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C33" s="37" t="s">
+    <row r="33" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C33" s="47" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="13">
@@ -2943,12 +3154,22 @@
       <c r="O33" s="13">
         <v>1</v>
       </c>
-      <c r="P33" s="34" t="s">
+      <c r="P33" s="44" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C34" s="39"/>
+      <c r="R33" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="S33" s="53"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="V33" s="53"/>
+      <c r="W33" s="10"/>
+    </row>
+    <row r="34" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C34" s="49"/>
       <c r="D34" s="11" t="s">
         <v>89</v>
       </c>
@@ -2985,10 +3206,16 @@
       <c r="O34" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="P34" s="35"/>
-    </row>
-    <row r="35" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C35" s="39"/>
+      <c r="P34" s="45"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+    </row>
+    <row r="35" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C35" s="49"/>
       <c r="D35" s="11" t="s">
         <v>87</v>
       </c>
@@ -3025,9 +3252,25 @@
       <c r="O35" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="P35" s="36"/>
-    </row>
-    <row r="36" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P35" s="46"/>
+      <c r="R35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="S35" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="V35" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="W35" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="36" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C36" s="14">
         <v>1</v>
       </c>
@@ -3048,8 +3291,24 @@
       <c r="P36" s="15">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R36" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="T36" s="10"/>
+      <c r="U36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C37" s="14">
         <v>2</v>
       </c>
@@ -3072,8 +3331,24 @@
       <c r="P37" s="15">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R37" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="T37" s="10"/>
+      <c r="U37" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C38" s="14">
         <v>3</v>
       </c>
@@ -3098,8 +3373,24 @@
       <c r="P38" s="15">
         <v>809</v>
       </c>
-    </row>
-    <row r="39" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R38" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="T38" s="10"/>
+      <c r="U38" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C39" s="14">
         <v>4</v>
       </c>
@@ -3122,8 +3413,24 @@
       <c r="P39" s="15">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R39" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="T39" s="10"/>
+      <c r="U39" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C40" s="14">
         <v>5</v>
       </c>
@@ -3148,8 +3455,24 @@
       <c r="P40" s="15">
         <v>414</v>
       </c>
-    </row>
-    <row r="41" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R40" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="T40" s="10"/>
+      <c r="U40" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="41" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C41" s="14">
         <v>6</v>
       </c>
@@ -3176,8 +3499,24 @@
       <c r="P41" s="15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R41" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="T41" s="10"/>
+      <c r="U41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="42" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C42" s="14">
         <v>7</v>
       </c>
@@ -3202,8 +3541,24 @@
       <c r="P42" s="15">
         <v>448</v>
       </c>
-    </row>
-    <row r="43" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R42" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="T42" s="10"/>
+      <c r="U42" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="43" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C43" s="14">
         <v>8</v>
       </c>
@@ -3224,8 +3579,24 @@
       <c r="P43" s="15">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="R43" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="T43" s="10"/>
+      <c r="U43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C44" s="14">
         <v>9</v>
       </c>
@@ -3242,8 +3613,24 @@
       <c r="N44" s="11"/>
       <c r="O44" s="11"/>
       <c r="P44" s="15"/>
-    </row>
-    <row r="45" spans="3:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R44" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="T44" s="10"/>
+      <c r="U44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="3:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C45" s="16">
         <v>10</v>
       </c>
@@ -3260,351 +3647,450 @@
       <c r="N45" s="17"/>
       <c r="O45" s="17"/>
       <c r="P45" s="19"/>
-    </row>
-    <row r="48" spans="3:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D49" s="44" t="s">
+      <c r="R45" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="T45" s="10"/>
+      <c r="U45" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="R46" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="T46" s="10"/>
+      <c r="U46" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="47" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="R47" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="T47" s="10"/>
+      <c r="U47" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="48" spans="3:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R48" s="39" t="s">
+        <v>355</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="T48" s="10"/>
+      <c r="U48" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="V48" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D49" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="E49" s="47" t="s">
+      <c r="E49" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="F49" s="43"/>
-      <c r="G49" s="50" t="s">
+      <c r="F49" s="34"/>
+      <c r="G49" s="41" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D50" s="45" t="s">
+      <c r="R49" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="S49" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="T49" s="10"/>
+      <c r="U49" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W49" s="1"/>
+    </row>
+    <row r="50" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D50" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F50" s="10"/>
-      <c r="G50" s="51" t="s">
+      <c r="G50" s="42" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D51" s="45" t="s">
+      <c r="R50" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="S50" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="T50" s="10"/>
+      <c r="U50" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W50" s="1"/>
+    </row>
+    <row r="51" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D51" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F51" s="10"/>
-      <c r="G51" s="51" t="s">
+      <c r="G51" s="42" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D52" s="45" t="s">
+    <row r="52" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D52" s="36" t="s">
         <v>262</v>
       </c>
-      <c r="E52" s="48" t="s">
+      <c r="E52" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F52" s="10"/>
-      <c r="G52" s="51" t="s">
+      <c r="G52" s="42" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D53" s="45" t="s">
+    <row r="53" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D53" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F53" s="10"/>
-      <c r="G53" s="51" t="s">
+      <c r="G53" s="42" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D54" s="45" t="s">
+    <row r="54" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D54" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="E54" s="48" t="s">
+      <c r="E54" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F54" s="10"/>
-      <c r="G54" s="51" t="s">
+      <c r="G54" s="42" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D55" s="45" t="s">
+    <row r="55" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D55" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="E55" s="48" t="s">
+      <c r="E55" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F55" s="10"/>
-      <c r="G55" s="51" t="s">
+      <c r="G55" s="42" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D56" s="45" t="s">
+    <row r="56" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D56" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="E56" s="48" t="s">
+      <c r="E56" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F56" s="10"/>
-      <c r="G56" s="51" t="s">
+      <c r="G56" s="42" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D57" s="45" t="s">
+    <row r="57" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D57" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F57" s="10"/>
-      <c r="G57" s="51" t="s">
+      <c r="G57" s="42" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D58" s="45" t="s">
+    <row r="58" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D58" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="E58" s="48" t="s">
+      <c r="E58" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F58" s="10"/>
-      <c r="G58" s="51" t="s">
+      <c r="G58" s="42" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D59" s="45" t="s">
+    <row r="59" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D59" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="E59" s="48" t="s">
+      <c r="E59" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F59" s="10"/>
-      <c r="G59" s="51" t="s">
+      <c r="G59" s="42" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="60" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D60" s="45" t="s">
+    <row r="60" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D60" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="E60" s="48" t="s">
+      <c r="E60" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F60" s="10"/>
-      <c r="G60" s="51" t="s">
+      <c r="G60" s="42" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="61" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D61" s="45" t="s">
+    <row r="61" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D61" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="E61" s="48" t="s">
+      <c r="E61" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F61" s="10"/>
-      <c r="G61" s="51" t="s">
+      <c r="G61" s="42" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="62" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D62" s="45" t="s">
+    <row r="62" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D62" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F62" s="10"/>
-      <c r="G62" s="51" t="s">
+      <c r="G62" s="42" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="63" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D63" s="45" t="s">
+    <row r="63" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D63" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="E63" s="48" t="s">
+      <c r="E63" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F63" s="10"/>
-      <c r="G63" s="51" t="s">
+      <c r="G63" s="42" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D64" s="45" t="s">
+    <row r="64" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D64" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F64" s="10"/>
-      <c r="G64" s="51" t="s">
+      <c r="G64" s="42" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="65" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D65" s="45" t="s">
+      <c r="D65" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F65" s="10"/>
-      <c r="G65" s="51" t="s">
+      <c r="G65" s="42" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="66" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D66" s="45" t="s">
+      <c r="D66" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F66" s="10"/>
-      <c r="G66" s="51" t="s">
+      <c r="G66" s="42" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="67" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D67" s="45" t="s">
+      <c r="D67" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="E67" s="48" t="s">
+      <c r="E67" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F67" s="10"/>
-      <c r="G67" s="51" t="s">
+      <c r="G67" s="42" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="68" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D68" s="45" t="s">
+      <c r="D68" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="E68" s="48" t="s">
+      <c r="E68" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F68" s="10"/>
-      <c r="G68" s="51" t="s">
+      <c r="G68" s="42" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="69" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D69" s="45" t="s">
+      <c r="D69" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="E69" s="48" t="s">
+      <c r="E69" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F69" s="10"/>
-      <c r="G69" s="51" t="s">
+      <c r="G69" s="42" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="70" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D70" s="45" t="s">
+      <c r="D70" s="36" t="s">
         <v>298</v>
       </c>
-      <c r="E70" s="48" t="s">
+      <c r="E70" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F70" s="10"/>
-      <c r="G70" s="51" t="s">
+      <c r="G70" s="42" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="71" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D71" s="45" t="s">
+      <c r="D71" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="E71" s="48" t="s">
+      <c r="E71" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F71" s="10"/>
-      <c r="G71" s="51" t="s">
+      <c r="G71" s="42" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="72" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D72" s="45" t="s">
+      <c r="D72" s="36" t="s">
         <v>302</v>
       </c>
-      <c r="E72" s="48" t="s">
+      <c r="E72" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F72" s="10"/>
-      <c r="G72" s="51" t="s">
+      <c r="G72" s="42" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="73" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D73" s="45" t="s">
+      <c r="D73" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="E73" s="48" t="s">
+      <c r="E73" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F73" s="10"/>
-      <c r="G73" s="51" t="s">
+      <c r="G73" s="42" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="74" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D74" s="45" t="s">
+      <c r="D74" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="E74" s="48" t="s">
+      <c r="E74" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F74" s="10"/>
-      <c r="G74" s="51" t="s">
+      <c r="G74" s="42" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="75" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D75" s="45" t="s">
+      <c r="D75" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="E75" s="48" t="s">
+      <c r="E75" s="39" t="s">
         <v>256</v>
       </c>
       <c r="F75" s="10"/>
-      <c r="G75" s="51" t="s">
+      <c r="G75" s="42" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="76" spans="4:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D76" s="46" t="s">
+      <c r="D76" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="E76" s="49" t="s">
+      <c r="E76" s="40" t="s">
         <v>256</v>
       </c>
       <c r="F76" s="3"/>
-      <c r="G76" s="52" t="s">
+      <c r="G76" s="43" t="s">
         <v>311</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="P33:P35"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="J4:V4"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="U33:V33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
